--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484234_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484234_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8767</v>
+        <v>6.0577</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5266</v>
+        <v>1.9302</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3501</v>
+        <v>4.1276</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.5522</v>
+        <v>0.6076</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9294</v>
+        <v>-0.9028</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.4816</v>
+        <v>1.5105</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.5881</v>
+        <v>-0.5211</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6792</v>
+        <v>-1.2229</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.2673</v>
+        <v>0.7017</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9641</v>
+        <v>1.1288</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2502</v>
+        <v>0.3201</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.2144</v>
+        <v>0.8087</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1488</v>
+        <v>2.7348</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1488</v>
+        <v>2.7348</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6792</v>
+        <v>0.3329</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5137</v>
+        <v>0.0689</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1655</v>
+        <v>0.264</v>
       </c>
       <c r="V2" t="n">
-        <v>3.601</v>
+        <v>2.3824</v>
       </c>
       <c r="W2" t="n">
-        <v>3.601</v>
+        <v>2.3824</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1993</v>
+        <v>6.0554</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3441</v>
+        <v>4.787</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8552</v>
+        <v>1.2684</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6076</v>
+        <v>-1.5522</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9028</v>
+        <v>0.9294</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5105</v>
+        <v>-2.4816</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5211</v>
+        <v>-0.5881</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.2229</v>
+        <v>0.6792</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7017</v>
+        <v>-1.2673</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1288</v>
+        <v>-0.9641</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3201</v>
+        <v>0.2502</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8087</v>
+        <v>-1.2144</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7348</v>
+        <v>2.1488</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7348</v>
+        <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5255</v>
+        <v>1.8578</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5172</v>
+        <v>1.7741</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0083</v>
+        <v>0.0838</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3824</v>
+        <v>3.601</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3824</v>
+        <v>3.601</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7155</v>
+        <v>4.371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8078</v>
+        <v>0.862</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9078</v>
+        <v>3.509</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4788</v>
+        <v>6.2177</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8294</v>
+        <v>4.9765</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3506</v>
+        <v>1.2412</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6635</v>
+        <v>5.4985</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2843</v>
+        <v>4.2569</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6208</v>
+        <v>1.2416</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1846</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4549</v>
+        <v>0.7197</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2702</v>
+        <v>-0.0004</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7581</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>-5.8603</v>
       </c>
       <c r="R4" t="n">
         <v>2.7348</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9404</v>
+        <v>0.447</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.3921</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0117</v>
+        <v>0.0549</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4959</v>
+        <v>0.8317</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4959</v>
+        <v>0.8317</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5652</v>
+        <v>3.9843</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0034</v>
+        <v>1.1311</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5686</v>
+        <v>2.8533</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6286</v>
+        <v>-0.4788</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6692</v>
+        <v>-0.8294</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0407</v>
+        <v>0.3506</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6486</v>
+        <v>-0.6635</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5538</v>
+        <v>-1.2843</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.6208</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02</v>
+        <v>0.1846</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1154</v>
+        <v>0.4549</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1354</v>
+        <v>-0.2702</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1488</v>
+        <v>2.7348</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7877999999999999</v>
+        <v>1.2092</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.652</v>
+        <v>1.2754</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4398</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3588</v>
+        <v>3.5387</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0133</v>
+        <v>0.5421</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3455</v>
+        <v>2.9966</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2177</v>
+        <v>0.6286</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9765</v>
+        <v>0.6692</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2412</v>
+        <v>-0.0407</v>
       </c>
       <c r="J6" t="n">
-        <v>5.4985</v>
+        <v>0.6486</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2569</v>
+        <v>0.5538</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2416</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7193000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7197</v>
+        <v>0.1154</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0004</v>
+        <v>-0.1354</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.1255</v>
+        <v>2.1488</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.8603</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7348</v>
+        <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5652</v>
+        <v>0.7613</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4566</v>
+        <v>-0.1065</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1085</v>
+        <v>0.8679</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. VERA CUSCOLL</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9506</v>
+        <v>3.3401</v>
       </c>
       <c r="E7" t="n">
-        <v>0.196</v>
+        <v>2.5462</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7547</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2838</v>
+        <v>2.0379</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3221</v>
+        <v>2.173</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0383</v>
+        <v>-0.135</v>
       </c>
       <c r="J7" t="n">
-        <v>0.35</v>
+        <v>1.5784</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6577</v>
+        <v>2.2525</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3077</v>
+        <v>-0.6741</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9338</v>
+        <v>0.4595</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6644</v>
+        <v>-0.0795</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2694</v>
+        <v>0.5391</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>0.186</v>
+        <v>0.3487</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.154</v>
+        <v>0.3584</v>
       </c>
       <c r="U7" t="n">
-        <v>0.34</v>
+        <v>-0.0097</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>E. VERA CUSCOLL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.9068</v>
+        <v>3.2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4961</v>
+        <v>0.4181</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4107</v>
+        <v>2.7819</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6865</v>
+        <v>1.2838</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9317</v>
+        <v>2.3221</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7548</v>
+        <v>-1.0383</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6766</v>
+        <v>1.6577</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0809</v>
+        <v>-1.3077</v>
       </c>
       <c r="M8" t="n">
-        <v>0.929</v>
+        <v>0.9338</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2551</v>
+        <v>0.6644</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.2694</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3924</v>
+        <v>0.4353</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4733</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.081</v>
+        <v>0.3672</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2661</v>
+        <v>2.9485</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7173</v>
+        <v>0.3743</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5488</v>
+        <v>2.5742</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0379</v>
+        <v>1.6865</v>
       </c>
       <c r="H9" t="n">
-        <v>2.173</v>
+        <v>0.9317</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.135</v>
+        <v>0.7548</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5784</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2525</v>
+        <v>0.6766</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6741</v>
+        <v>0.0809</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4595</v>
+        <v>0.929</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0795</v>
+        <v>0.2551</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5391</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5627</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
         <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7252</v>
+        <v>0.434</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4704</v>
+        <v>0.3516</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2548</v>
+        <v>0.0824</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.0198</v>
+        <v>2.6852</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1193</v>
+        <v>2.9481</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.2629</v>
       </c>
       <c r="G10" t="n">
         <v>3.9652</v>
@@ -1234,13 +1234,13 @@
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0313</v>
+        <v>0.6967</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3494</v>
+        <v>0.4795</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3807</v>
+        <v>0.2173</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6093</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1387</v>
+        <v>-0.8368</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0365</v>
+        <v>-0.8738</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1022</v>
+        <v>0.037</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3761</v>
+        <v>-1.2215</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3935</v>
+        <v>-1.1003</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9826</v>
+        <v>-0.1212</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0174</v>
+        <v>-0.2624</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3838</v>
+        <v>-0.8161</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.5537</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3587</v>
+        <v>-0.9591</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0097</v>
+        <v>-0.2842</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.349</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9055</v>
+        <v>0.4313</v>
       </c>
       <c r="T11" t="n">
-        <v>3.0074</v>
+        <v>0.3653</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1018</v>
+        <v>0.0659</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5285</v>
+        <v>-1.2164</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8782</v>
+        <v>-1.3186</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3498</v>
+        <v>0.1022</v>
       </c>
       <c r="G12" t="n">
-        <v>0.433</v>
+        <v>-2.3761</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0422</v>
+        <v>-0.3935</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3908</v>
+        <v>-1.9826</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1613</v>
+        <v>-1.0174</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2827</v>
+        <v>-0.3838</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1214</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5944</v>
+        <v>-1.3587</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3249</v>
+        <v>-0.0097</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2694</v>
+        <v>-1.349</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1488</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7417</v>
+        <v>1.5504</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1899</v>
+        <v>1.6523</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5518</v>
+        <v>-0.1018</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9768</v>
+        <v>-1.8197</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9049</v>
+        <v>-4.0605</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.07190000000000001</v>
+        <v>2.2408</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.2215</v>
+        <v>0.433</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1003</v>
+        <v>0.0422</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1212</v>
+        <v>0.3908</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2624</v>
+        <v>-0.1613</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.8161</v>
+        <v>-0.2827</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5537</v>
+        <v>0.1214</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9591</v>
+        <v>0.5944</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2842</v>
+        <v>0.3249</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.2694</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7087</v>
+        <v>0.4505</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6657</v>
+        <v>0.0076</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.043</v>
+        <v>0.4429</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>30.4922</v>
+        <v>32.30800000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>7.470499999999999</v>
+        <v>9.286200000000001</v>
       </c>
       <c r="F14" t="n">
         <v>23.022</v>
@@ -1522,13 +1522,13 @@
         <v>10.4088</v>
       </c>
       <c r="K14" t="n">
-        <v>7.706199999999999</v>
+        <v>7.706199999999998</v>
       </c>
       <c r="L14" t="n">
         <v>2.7022</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8231999999999998</v>
+        <v>0.8231999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>2.8516</v>
@@ -1546,16 +1546,16 @@
         <v>24.4178</v>
       </c>
       <c r="S14" t="n">
-        <v>7.139699999999999</v>
+        <v>8.9551</v>
       </c>
       <c r="T14" t="n">
-        <v>4.871099999999999</v>
+        <v>6.686800000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2687</v>
+        <v>2.2686</v>
       </c>
       <c r="V14" t="n">
-        <v>6.2607</v>
+        <v>6.260700000000001</v>
       </c>
       <c r="W14" t="n">
         <v>10.7482</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8121</v>
+        <v>2.4335</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0939</v>
+        <v>3.6895</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2818</v>
+        <v>-1.256</v>
       </c>
       <c r="G15" t="n">
         <v>1.1815</v>
@@ -1624,13 +1624,13 @@
         <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1227</v>
+        <v>-0.2559</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5284</v>
+        <v>0.124</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4057</v>
+        <v>-0.3798</v>
       </c>
       <c r="V15" t="n">
         <v>-0.0549</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0034</v>
+        <v>0.2782</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5437</v>
+        <v>0.8471</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5403</v>
+        <v>-0.5689</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2661</v>
@@ -1702,13 +1702,13 @@
         <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1408</v>
+        <v>-0.866</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7922</v>
+        <v>-0.4889</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3485</v>
+        <v>-0.3771</v>
       </c>
       <c r="V16" t="n">
         <v>1.6056</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3926</v>
+        <v>-0.0335</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8541</v>
+        <v>-0.9553</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4615</v>
+        <v>0.9218</v>
       </c>
       <c r="G17" t="n">
         <v>1.3318</v>
@@ -1780,13 +1780,13 @@
         <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9431</v>
+        <v>-0.5839</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.0185</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0258</v>
+        <v>-0.5655</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0536</v>
+        <v>-1.357</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5186</v>
+        <v>-2.8219</v>
       </c>
       <c r="F18" t="n">
         <v>1.465</v>
@@ -1858,10 +1858,10 @@
         <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5531</v>
+        <v>0.2497</v>
       </c>
       <c r="T18" t="n">
-        <v>0.399</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="U18" t="n">
         <v>0.154</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3939</v>
+        <v>-1.4535</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4058</v>
+        <v>-1.7091</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0119</v>
+        <v>0.2556</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4611</v>
@@ -1936,13 +1936,13 @@
         <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1281</v>
+        <v>-0.1877</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1432</v>
+        <v>-0.1602</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2713</v>
+        <v>-0.0275</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9947</v>
+        <v>-1.7509</v>
       </c>
       <c r="E20" t="n">
         <v>-0.76</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2347</v>
+        <v>-0.9909</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0068</v>
@@ -2014,13 +2014,13 @@
         <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5739</v>
+        <v>-0.3302</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1678</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4061</v>
+        <v>-0.1624</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6093</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1452</v>
+        <v>-2.3954</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0413</v>
+        <v>-1.3447</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1038</v>
+        <v>-1.0507</v>
       </c>
       <c r="G21" t="n">
         <v>-2.216</v>
@@ -2092,13 +2092,13 @@
         <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2895</v>
+        <v>0.0392</v>
       </c>
       <c r="T21" t="n">
-        <v>0.311</v>
+        <v>0.0076</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0215</v>
+        <v>0.0316</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6093</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1703</v>
+        <v>-2.9408</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4496</v>
+        <v>-2.6518</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7207</v>
+        <v>-0.289</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4309</v>
@@ -2170,13 +2170,13 @@
         <v>2.7348</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.931</v>
+        <v>-0.7015</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.374</v>
+        <v>-0.5762</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.1253</v>
       </c>
       <c r="V22" t="n">
         <v>0.3869</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8997</v>
+        <v>-6.5303</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.8666</v>
+        <v>-5.361</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0331</v>
+        <v>-1.1692</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2812</v>
@@ -2248,13 +2248,13 @@
         <v>2.1488</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1226</v>
+        <v>-0.7532</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5447</v>
+        <v>-0.0391</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5779</v>
+        <v>-0.7141</v>
       </c>
       <c r="V23" t="n">
         <v>-2.7145</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.581</v>
+        <v>-6.7513</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.3845</v>
+        <v>-4.8789</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1966</v>
+        <v>-1.8724</v>
       </c>
       <c r="G24" t="n">
         <v>-3.041</v>
@@ -2326,13 +2326,13 @@
         <v>2.1488</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6888</v>
+        <v>-0.8591</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7592</v>
+        <v>-0.2537</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9296</v>
+        <v>-0.6054</v>
       </c>
       <c r="V24" t="n">
         <v>-3.0466</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.677</v>
+        <v>-7.9691</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.3791</v>
+        <v>-7.0757</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2979</v>
+        <v>-0.8934</v>
       </c>
       <c r="G25" t="n">
         <v>0.3692</v>
@@ -2404,13 +2404,13 @@
         <v>2.5395</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5765</v>
+        <v>-0.8687</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0948</v>
+        <v>-0.7915</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4817</v>
+        <v>-0.0772</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2186</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-30.4925</v>
+        <v>-28.4701</v>
       </c>
       <c r="E26" t="n">
-        <v>-23.022</v>
+        <v>-23.0218</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.4705</v>
+        <v>-5.4481</v>
       </c>
       <c r="G26" t="n">
         <v>-11.2319</v>
@@ -2482,13 +2482,13 @@
         <v>18.5578</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.139500000000001</v>
+        <v>-5.1173</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.2685</v>
+        <v>-2.2686</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.8711</v>
+        <v>-2.8487</v>
       </c>
       <c r="V26" t="n">
         <v>-6.2607</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484234_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484234_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,28 +819,28 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9843</v>
+        <v>3.6773</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1311</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>2.8533</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4788</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8294</v>
+        <v>-1.1364</v>
       </c>
       <c r="I5" t="n">
         <v>0.3506</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6635</v>
+        <v>-0.9704</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2843</v>
+        <v>-1.5912</v>
       </c>
       <c r="L5" t="n">
         <v>0.6208</v>
@@ -860,6 +880,11 @@
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1016,6 +1046,11 @@
       </c>
       <c r="X7" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,11 +1296,16 @@
       <c r="X10" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8368</v>
+        <v>0.307</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8738</v>
+        <v>0.307</v>
       </c>
       <c r="F11" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2215</v>
+        <v>0.307</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1003</v>
+        <v>0.307</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1212</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2624</v>
+        <v>0.307</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8161</v>
+        <v>0.307</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5537</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9591</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2842</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4313</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3653</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0659</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2164</v>
+        <v>-0.8368</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3186</v>
+        <v>-0.8738</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1022</v>
+        <v>0.037</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3761</v>
+        <v>-1.2215</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3935</v>
+        <v>-1.1003</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9826</v>
+        <v>-0.1212</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0174</v>
+        <v>-0.2624</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3838</v>
+        <v>-0.8161</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.5537</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3587</v>
+        <v>-0.9591</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0097</v>
+        <v>-0.2842</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.349</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5504</v>
+        <v>0.4313</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6523</v>
+        <v>0.3653</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1018</v>
+        <v>0.0659</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8197</v>
+        <v>-1.2164</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0605</v>
+        <v>-1.3186</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2408</v>
+        <v>0.1022</v>
       </c>
       <c r="G13" t="n">
-        <v>0.433</v>
+        <v>-2.3761</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0422</v>
+        <v>-0.3935</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3908</v>
+        <v>-1.9826</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1613</v>
+        <v>-1.0174</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2827</v>
+        <v>-0.3838</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1214</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5944</v>
+        <v>-1.3587</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3249</v>
+        <v>-0.0097</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2694</v>
+        <v>-1.349</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.1488</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4505</v>
+        <v>1.5504</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0076</v>
+        <v>1.6523</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4429</v>
+        <v>-0.1018</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,151 +1566,157 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>32.30800000000001</v>
+        <v>-1.8197</v>
       </c>
       <c r="E14" t="n">
-        <v>9.286200000000001</v>
+        <v>-4.0605</v>
       </c>
       <c r="F14" t="n">
-        <v>23.022</v>
+        <v>2.2408</v>
       </c>
       <c r="G14" t="n">
-        <v>11.2317</v>
+        <v>0.433</v>
       </c>
       <c r="H14" t="n">
-        <v>10.5577</v>
+        <v>0.0422</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6741000000000004</v>
+        <v>0.3908</v>
       </c>
       <c r="J14" t="n">
-        <v>10.4088</v>
+        <v>-0.1613</v>
       </c>
       <c r="K14" t="n">
-        <v>7.706199999999998</v>
+        <v>-0.2827</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7022</v>
+        <v>0.1214</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8231999999999999</v>
+        <v>0.5944</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8516</v>
+        <v>0.3249</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.0283</v>
+        <v>0.2694</v>
       </c>
       <c r="P14" t="n">
-        <v>5.860299999999999</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q14" t="n">
-        <v>-18.5575</v>
+        <v>-3.9069</v>
       </c>
       <c r="R14" t="n">
-        <v>24.4178</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>8.9551</v>
+        <v>0.4505</v>
       </c>
       <c r="T14" t="n">
-        <v>6.686800000000001</v>
+        <v>0.0076</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2686</v>
+        <v>0.4429</v>
       </c>
       <c r="V14" t="n">
-        <v>6.260700000000001</v>
+        <v>-0.5545</v>
       </c>
       <c r="W14" t="n">
-        <v>10.7482</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.4875</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4335</v>
+        <v>32.30800000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6895</v>
+        <v>9.286200000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.256</v>
+        <v>23.022</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1815</v>
+        <v>11.2317</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5344</v>
+        <v>10.5577</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6471</v>
+        <v>0.6741000000000004</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7691</v>
+        <v>10.4089</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3123</v>
+        <v>7.706299999999998</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4568</v>
+        <v>2.7022</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5876</v>
+        <v>0.8231999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7779</v>
+        <v>2.8516</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8097</v>
+        <v>-2.0283</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5627</v>
+        <v>5.860299999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-18.5575</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5395</v>
+        <v>24.4178</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2559</v>
+        <v>8.9551</v>
       </c>
       <c r="T15" t="n">
-        <v>0.124</v>
+        <v>6.686800000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3798</v>
+        <v>2.2686</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.0549</v>
+        <v>6.260700000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7731</v>
+        <v>10.7482</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8279</v>
-      </c>
+        <v>-4.4875</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2782</v>
+        <v>2.4335</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8471</v>
+        <v>3.6895</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5689</v>
+        <v>-1.256</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2661</v>
+        <v>1.1815</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1781</v>
+        <v>0.5344</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4441</v>
+        <v>0.6471</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8521</v>
+        <v>2.7691</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0258</v>
+        <v>1.3123</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1737</v>
+        <v>1.4568</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1182</v>
+        <v>-1.5876</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8478</v>
+        <v>-0.7779</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2704</v>
+        <v>-0.8097</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.866</v>
+        <v>-0.2559</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4889</v>
+        <v>0.124</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3771</v>
+        <v>-0.3798</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6056</v>
+        <v>-0.0549</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4373</v>
+        <v>1.7731</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8317</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. HUGUET CARRASCO</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0335</v>
+        <v>0.2782</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9553</v>
+        <v>0.8471</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9218</v>
+        <v>-0.5689</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3318</v>
+        <v>-0.2661</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0302</v>
+        <v>0.1781</v>
       </c>
       <c r="I17" t="n">
-        <v>1.362</v>
+        <v>-0.4441</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0166</v>
+        <v>0.8521</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3287</v>
+        <v>1.0258</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6879</v>
+        <v>-0.1737</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3152</v>
+        <v>-1.1182</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3589</v>
+        <v>-0.8478</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6741</v>
+        <v>-0.2704</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5839</v>
+        <v>-0.866</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0185</v>
+        <v>-0.4889</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5655</v>
+        <v>-0.3771</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.6056</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>L. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.357</v>
+        <v>-0.0335</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8219</v>
+        <v>-0.9553</v>
       </c>
       <c r="F18" t="n">
-        <v>1.465</v>
+        <v>0.9218</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4113</v>
+        <v>1.3318</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7214</v>
+        <v>-0.0302</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3101</v>
+        <v>1.362</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.9409</v>
+        <v>1.0166</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3073</v>
+        <v>0.3287</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.6879</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5296</v>
+        <v>0.3152</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4142</v>
+        <v>-0.3589</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9437</v>
+        <v>0.6741</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2497</v>
+        <v>-0.5839</v>
       </c>
       <c r="T18" t="n">
-        <v>0.09569999999999999</v>
+        <v>-0.0185</v>
       </c>
       <c r="U18" t="n">
-        <v>0.154</v>
+        <v>-0.5655</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1874,12 +1955,17 @@
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. COOPER SPACIR</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4535</v>
+        <v>-1.357</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7091</v>
+        <v>-2.8219</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2556</v>
+        <v>1.465</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4611</v>
+        <v>-1.4113</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0967</v>
+        <v>-1.7214</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3644</v>
+        <v>0.3101</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5722</v>
+        <v>-1.9409</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6127</v>
+        <v>-1.3073</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8889</v>
+        <v>0.5296</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.484</v>
+        <v>-0.4142</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4049</v>
+        <v>0.9437</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1877</v>
+        <v>0.2497</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1602</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0275</v>
+        <v>0.154</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,12 +2038,17 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DIAGNE YADE</t>
+          <t>D. COOPER SPACIR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7509</v>
+        <v>-1.4535</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.76</v>
+        <v>-1.7091</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9909</v>
+        <v>0.2556</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0068</v>
+        <v>-1.4611</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3323</v>
+        <v>-1.0967</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6745</v>
+        <v>-0.3644</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.5722</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0819</v>
+        <v>-0.6127</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6741</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4146</v>
+        <v>-0.8889</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4142</v>
+        <v>-0.484</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0004</v>
+        <v>-0.4049</v>
       </c>
       <c r="P20" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3302</v>
+        <v>-0.1877</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1678</v>
+        <v>-0.1602</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1624</v>
+        <v>-0.0275</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>A. DIAGNE YADE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3954</v>
+        <v>-1.7509</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3447</v>
+        <v>-0.76</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0507</v>
+        <v>-0.9909</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.216</v>
+        <v>-1.0068</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0361</v>
+        <v>-0.3323</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2521</v>
+        <v>-0.6745</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6528</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6549</v>
+        <v>0.0819</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3077</v>
+        <v>-0.6741</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5632</v>
+        <v>-0.4146</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6188</v>
+        <v>-0.4142</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9443</v>
+        <v>-0.0004</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0392</v>
+        <v>-0.3302</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0076</v>
+        <v>-0.1678</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0316</v>
+        <v>-0.1624</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6093</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8865</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9408</v>
+        <v>-2.3954</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6518</v>
+        <v>-1.3447</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.289</v>
+        <v>-1.0507</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4309</v>
+        <v>-2.216</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0414</v>
+        <v>0.0361</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3895</v>
+        <v>-2.2521</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8545</v>
+        <v>-0.6528</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7598</v>
+        <v>0.6549</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09470000000000001</v>
+        <v>-1.3077</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.2854</v>
+        <v>-1.5632</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8012</v>
+        <v>-0.6188</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4842</v>
+        <v>-0.9443</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7348</v>
+        <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7015</v>
+        <v>0.0392</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5762</v>
+        <v>0.0076</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1253</v>
+        <v>0.0316</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3869</v>
+        <v>-0.6093</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3869</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5303</v>
+        <v>-2.9408</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.361</v>
+        <v>-2.6518</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1692</v>
+        <v>-0.289</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2812</v>
+        <v>-2.4309</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.4835</v>
+        <v>-1.0414</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2023</v>
+        <v>-1.3895</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.3917</v>
+        <v>0.8545</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.92</v>
+        <v>0.7598</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4718</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1105</v>
+        <v>-3.2854</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5636</v>
+        <v>-1.8012</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6741</v>
+        <v>-1.4842</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1488</v>
+        <v>2.7348</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7532</v>
+        <v>-0.7015</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0391</v>
+        <v>-0.5762</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7141</v>
+        <v>-0.1253</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.7145</v>
+        <v>0.3869</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.7145</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>A. BENNASSAR ROSSELLO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.7513</v>
+        <v>-6.5303</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.8789</v>
+        <v>-5.361</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8724</v>
+        <v>-1.1692</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.041</v>
+        <v>-2.2812</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.1213</v>
+        <v>-2.4835</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0803</v>
+        <v>0.2023</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.6718</v>
+        <v>-2.3917</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.7527</v>
+        <v>-1.92</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0809</v>
+        <v>-0.4718</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3692</v>
+        <v>0.1105</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3686</v>
+        <v>-0.5636</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.6741</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R24" t="n">
         <v>2.1488</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8591</v>
+        <v>-0.7532</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2537</v>
+        <v>-0.0391</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6054</v>
+        <v>-0.7141</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.0466</v>
+        <v>-2.7145</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.0466</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.9691</v>
+        <v>-6.7513</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.0757</v>
+        <v>-4.8789</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8934</v>
+        <v>-1.8724</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3692</v>
+        <v>-3.041</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.4794</v>
+        <v>-3.1213</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8486</v>
+        <v>0.0803</v>
       </c>
       <c r="J25" t="n">
-        <v>2.5062</v>
+        <v>-2.6718</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4222</v>
+        <v>-2.7527</v>
       </c>
       <c r="L25" t="n">
-        <v>2.9283</v>
+        <v>0.0809</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.137</v>
+        <v>-0.3692</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0573</v>
+        <v>-0.3686</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0797</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-6.251</v>
+        <v>0.1953</v>
       </c>
       <c r="Q25" t="n">
-        <v>-8.7904</v>
+        <v>-1.9534</v>
       </c>
       <c r="R25" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8687</v>
+        <v>-0.8591</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7915</v>
+        <v>-0.2537</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0772</v>
+        <v>-0.6054</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2186</v>
+        <v>-3.0466</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2186</v>
+        <v>-3.0466</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,152 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-7.9691</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-7.0757</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.8934</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.4794</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.8486</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.5062</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.4222</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2.9283</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.137</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.0573</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.0797</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-6.251</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-8.7904</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.8687</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.7915</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.0772</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484234_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>-28.4701</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E27" t="n">
         <v>-23.0218</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>-5.4481</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G27" t="n">
         <v>-11.2319</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H27" t="n">
         <v>-10.5576</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>-0.6742000000000001</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>-0.8231000000000006</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K27" t="n">
         <v>-2.8515</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>2.0282</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>-10.4088</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N27" t="n">
         <v>-7.7065</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O27" t="n">
         <v>-2.7023</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P27" t="n">
         <v>-5.8604</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q27" t="n">
         <v>-24.4176</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>18.5578</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S27" t="n">
         <v>-5.1173</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>-2.2686</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>-2.8487</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V27" t="n">
         <v>-6.2607</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W27" t="n">
         <v>4.4876</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X27" t="n">
         <v>-10.7482</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
